--- a/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por limpieza de boca</t>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 15,66</t>
+          <t>2,86; 15,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 12,06</t>
+          <t>1,16; 11,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,78; 28,49</t>
+          <t>9,5; 27,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,62; 37,8</t>
+          <t>20,16; 39,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,2</t>
+          <t>1,34; 11,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 26,13</t>
+          <t>6,62; 24,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 23,77</t>
+          <t>7,32; 24,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 37,88</t>
+          <t>21,52; 38,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 10,8</t>
+          <t>2,76; 11,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 15,35</t>
+          <t>4,46; 14,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 22,03</t>
+          <t>10,71; 22,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 35,18</t>
+          <t>22,67; 34,96</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 14,25</t>
+          <t>1,14; 13,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,99</t>
+          <t>1,27; 12,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 25,13</t>
+          <t>9,76; 26,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 41,67</t>
+          <t>22,43; 41,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 24,15</t>
+          <t>5,58; 24,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,65</t>
+          <t>2,25; 14,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 25,41</t>
+          <t>9,72; 27,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,22; 36,01</t>
+          <t>19,02; 37,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 15,82</t>
+          <t>4,92; 15,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,98</t>
+          <t>2,02; 10,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 23,44</t>
+          <t>10,6; 23,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 37,5</t>
+          <t>22,68; 36,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,34</t>
+          <t>0,0; 9,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 23,0</t>
+          <t>4,6; 21,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,86; 49,68</t>
+          <t>16,84; 50,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,44</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,01</t>
+          <t>1,58; 14,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 27,75</t>
+          <t>6,47; 27,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,44; 50,7</t>
+          <t>21,91; 49,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,82</t>
+          <t>0,6; 5,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,69</t>
+          <t>0,82; 8,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,63; 21,44</t>
+          <t>7,82; 21,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,04; 44,93</t>
+          <t>24,28; 46,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 14,92</t>
+          <t>4,67; 13,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,66</t>
+          <t>5,05; 15,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,4; 25,89</t>
+          <t>13,41; 25,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 31,66</t>
+          <t>16,38; 31,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,61</t>
+          <t>1,98; 9,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 12,41</t>
+          <t>3,44; 12,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 27,62</t>
+          <t>13,75; 27,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,38; 38,07</t>
+          <t>20,38; 37,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,8</t>
+          <t>4,46; 10,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 12,11</t>
+          <t>5,24; 12,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 24,36</t>
+          <t>15,31; 24,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 31,8</t>
+          <t>20,19; 31,97</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 19,84</t>
+          <t>5,81; 19,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,28</t>
+          <t>1,95; 9,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 30,1</t>
+          <t>14,01; 29,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,08; 37,24</t>
+          <t>19,07; 37,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,76</t>
+          <t>4,54; 15,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,8</t>
+          <t>1,69; 10,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 33,72</t>
+          <t>15,6; 32,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,46; 43,09</t>
+          <t>21,44; 43,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 15,29</t>
+          <t>6,27; 15,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,31</t>
+          <t>2,44; 8,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,59; 29,11</t>
+          <t>17,96; 29,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,58; 38,16</t>
+          <t>23,6; 38,77</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 12,76</t>
+          <t>1,13; 12,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 23,98</t>
+          <t>2,7; 24,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 38,85</t>
+          <t>13,09; 37,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,04; 56,02</t>
+          <t>30,41; 56,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 17,18</t>
+          <t>1,9; 17,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 12,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 34,88</t>
+          <t>10,99; 36,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,73; 65,34</t>
+          <t>34,12; 62,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,8</t>
+          <t>2,51; 11,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,46</t>
+          <t>2,15; 12,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,48; 32,59</t>
+          <t>14,84; 33,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,08; 56,2</t>
+          <t>36,94; 55,66</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,0</t>
+          <t>5,08; 9,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,02</t>
+          <t>3,96; 8,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,28</t>
+          <t>15,31; 22,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 33,55</t>
+          <t>25,33; 33,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,64</t>
+          <t>4,46; 9,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,37</t>
+          <t>4,43; 8,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 23,05</t>
+          <t>15,77; 22,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,07; 35,89</t>
+          <t>27,16; 35,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,44</t>
+          <t>5,37; 8,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,05</t>
+          <t>4,79; 7,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,51</t>
+          <t>16,47; 21,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,81; 34,12</t>
+          <t>27,64; 33,41</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por limpieza de boca (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4314</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7648</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20379</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>27544</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6354</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8099</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14663</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>47923</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1566; 8414</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>559; 5587</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4085; 12024</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14470; 28018</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>663; 5429</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2706; 10054</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3697; 12231</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>20675; 36738</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2876; 11763</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3972; 13215</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10020; 21483</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>38061; 58683</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2148</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8981</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19438</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>5194</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18055</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>39124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>461; 5587</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>604; 5705</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5438; 14780</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14063; 26107</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2068; 9052</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1196; 7657</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5253; 14957</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>13617; 27022</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3813; 12383</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2027; 10132</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11632; 25329</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>30455; 48672</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3579</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8701</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>12946</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8736</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>21647</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2935</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3872</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1433; 6805</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4704; 13964</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4570</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>628; 5761</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2218; 9583</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7943; 18005</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>531; 5012</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>669; 7204</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5116; 13957</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>15584; 29602</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8611</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21045</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25749</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20643</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>35121</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13115</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15342</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>41688</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>60870</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4579; 13662</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4608; 13916</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14904; 28012</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>18193; 34638</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1900; 8749</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3371; 12058</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14284; 28825</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>25962; 47746</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8664; 19747</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9908; 22796</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>32907; 52223</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>48139; 76221</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6580</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14611</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19072</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6249</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18234</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>33877</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12829</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7278</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>32845</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>52950</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3173; 10775</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1599; 7795</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9687; 20452</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13059; 25777</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3182; 10897</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1244; 7777</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11479; 24230</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>22129; 45326</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>7822; 18708</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3811; 12802</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25635; 41724</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>40528; 66575</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2247</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7745</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19719</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>21678</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4354</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14364</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>41397</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>454; 4806</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>673; 6075</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4267; 12341</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>13643; 25540</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>679; 6164</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4621</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3539; 11749</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>15057; 27453</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1901; 8656</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1343; 7790</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9616; 21694</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>32879; 49539</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>23661</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>19752</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>63609</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>113307</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21888</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22557</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>66743</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>150605</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>45549</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>42310</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>130351</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>263911</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>16400; 32157</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>13301; 27737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>52474; 76550</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>97962; 130127</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15254; 30745</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>15175; 30432</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>54971; 79762</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>130012; 172178</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>35672; 55962</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>32507; 53488</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>113856; 149223</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>239240; 289143</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,36</t>
+          <t>2,85; 15,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,58</t>
+          <t>1,17; 11,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 27,95</t>
+          <t>9,85; 29,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,16; 39,04</t>
+          <t>19,25; 38,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 24,59</t>
+          <t>6,61; 25,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 24,21</t>
+          <t>7,43; 23,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 38,23</t>
+          <t>21,01; 38,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,29</t>
+          <t>2,78; 10,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 14,83</t>
+          <t>5,06; 15,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 22,97</t>
+          <t>10,03; 22,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,67; 34,96</t>
+          <t>22,59; 34,99</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,79</t>
+          <t>1,14; 13,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,01</t>
+          <t>1,29; 11,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 26,52</t>
+          <t>8,76; 25,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,43; 41,64</t>
+          <t>22,14; 41,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 24,43</t>
+          <t>6,7; 25,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 14,43</t>
+          <t>1,29; 15,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 27,68</t>
+          <t>9,22; 26,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 37,75</t>
+          <t>18,8; 36,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 15,97</t>
+          <t>4,9; 15,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 10,07</t>
+          <t>2,09; 9,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 23,08</t>
+          <t>11,21; 22,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,68; 36,24</t>
+          <t>23,32; 36,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>0,0; 9,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 21,86</t>
+          <t>5,15; 24,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 50,0</t>
+          <t>17,93; 48,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 7,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,48</t>
+          <t>1,57; 13,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 27,94</t>
+          <t>6,63; 28,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,91; 49,66</t>
+          <t>21,99; 51,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,67</t>
+          <t>0,61; 5,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,84</t>
+          <t>0,94; 7,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 21,33</t>
+          <t>6,94; 21,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,28; 46,12</t>
+          <t>23,02; 44,48</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 13,92</t>
+          <t>4,67; 14,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 15,25</t>
+          <t>4,89; 15,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 25,21</t>
+          <t>13,68; 25,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,38; 31,19</t>
+          <t>16,3; 31,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,1</t>
+          <t>2,05; 9,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 12,31</t>
+          <t>3,26; 12,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 27,75</t>
+          <t>13,8; 26,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,38; 37,48</t>
+          <t>19,87; 37,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,16</t>
+          <t>4,37; 10,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,05</t>
+          <t>5,29; 12,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,31; 24,29</t>
+          <t>15,34; 24,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 31,97</t>
+          <t>20,47; 31,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,81; 19,71</t>
+          <t>6,08; 20,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 9,48</t>
+          <t>1,75; 9,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,01; 29,57</t>
+          <t>13,81; 29,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 37,63</t>
+          <t>19,62; 38,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 15,56</t>
+          <t>4,17; 15,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,56</t>
+          <t>1,72; 10,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,6; 32,93</t>
+          <t>16,88; 34,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,44; 43,92</t>
+          <t>20,56; 43,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,0</t>
+          <t>6,76; 15,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 8,21</t>
+          <t>2,43; 8,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 29,23</t>
+          <t>17,25; 29,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,6; 38,77</t>
+          <t>22,99; 38,37</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 12,01</t>
+          <t>1,13; 12,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 24,35</t>
+          <t>2,66; 23,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,09; 37,86</t>
+          <t>13,65; 38,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,41; 56,93</t>
+          <t>31,76; 57,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,25</t>
+          <t>1,99; 18,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 12,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 36,5</t>
+          <t>9,37; 36,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,12; 62,2</t>
+          <t>36,41; 64,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,43</t>
+          <t>2,41; 10,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,47</t>
+          <t>2,12; 12,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,84; 33,48</t>
+          <t>13,98; 31,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,94; 55,66</t>
+          <t>36,58; 56,28</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,95</t>
+          <t>5,23; 9,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,26</t>
+          <t>4,15; 8,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,33</t>
+          <t>15,34; 22,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,33; 33,64</t>
+          <t>25,3; 33,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,0</t>
+          <t>4,48; 8,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,87</t>
+          <t>4,45; 8,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,89</t>
+          <t>15,92; 22,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,16; 35,97</t>
+          <t>27,33; 36,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,42</t>
+          <t>5,41; 8,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,88</t>
+          <t>4,9; 7,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,47; 21,59</t>
+          <t>16,6; 21,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,64; 33,41</t>
+          <t>27,77; 33,43</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1566; 8414</t>
+          <t>1563; 8417</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>559; 5587</t>
+          <t>566; 5657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4085; 12024</t>
+          <t>4239; 12475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14470; 28018</t>
+          <t>13818; 27907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>663; 5429</t>
+          <t>660; 5430</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2706; 10054</t>
+          <t>2704; 10458</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3697; 12231</t>
+          <t>3754; 11908</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20675; 36738</t>
+          <t>20190; 36659</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2876; 11763</t>
+          <t>2898; 11285</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3972; 13215</t>
+          <t>4506; 13664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10020; 21483</t>
+          <t>9379; 21348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38061; 58683</t>
+          <t>37925; 58744</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>461; 5587</t>
+          <t>463; 5342</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>604; 5705</t>
+          <t>612; 5473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5438; 14780</t>
+          <t>4885; 14152</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14063; 26107</t>
+          <t>13884; 26313</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2068; 9052</t>
+          <t>2483; 9363</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1196; 7657</t>
+          <t>685; 8183</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5253; 14957</t>
+          <t>4980; 14486</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13617; 27022</t>
+          <t>13455; 26354</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3813; 12383</t>
+          <t>3799; 12165</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2027; 10132</t>
+          <t>2101; 10031</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11632; 25329</t>
+          <t>12301; 25053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30455; 48672</t>
+          <t>31317; 49038</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 2773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3872</t>
+          <t>0; 3841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1433; 6805</t>
+          <t>1604; 7488</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4704; 13964</t>
+          <t>5006; 13565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4570</t>
+          <t>0; 4105</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>628; 5761</t>
+          <t>626; 5490</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2218; 9583</t>
+          <t>2276; 9828</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7943; 18005</t>
+          <t>7973; 18849</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531; 5012</t>
+          <t>538; 5037</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>669; 7204</t>
+          <t>766; 6407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5116; 13957</t>
+          <t>4538; 13761</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15584; 29602</t>
+          <t>14777; 28550</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4579; 13662</t>
+          <t>4586; 14591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4608; 13916</t>
+          <t>4464; 14467</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14904; 28012</t>
+          <t>15200; 28643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18193; 34638</t>
+          <t>18105; 35000</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1900; 8749</t>
+          <t>1969; 8809</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3371; 12058</t>
+          <t>3197; 12471</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14284; 28825</t>
+          <t>14334; 27719</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25962; 47746</t>
+          <t>25310; 47412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8664; 19747</t>
+          <t>8481; 20498</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9908; 22796</t>
+          <t>10006; 23634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32907; 52223</t>
+          <t>32973; 52350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48139; 76221</t>
+          <t>48820; 75478</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3173; 10775</t>
+          <t>3324; 11153</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1599; 7795</t>
+          <t>1441; 8129</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9687; 20452</t>
+          <t>9551; 20244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13059; 25777</t>
+          <t>13439; 26059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3182; 10897</t>
+          <t>2918; 11106</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1244; 7777</t>
+          <t>1269; 8003</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11479; 24230</t>
+          <t>12421; 25125</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22129; 45326</t>
+          <t>21221; 44497</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7822; 18708</t>
+          <t>8428; 19200</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3811; 12802</t>
+          <t>3790; 13095</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25635; 41724</t>
+          <t>24624; 41482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>40528; 66575</t>
+          <t>39481; 65880</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>454; 4806</t>
+          <t>454; 4843</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>673; 6075</t>
+          <t>662; 5875</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4267; 12341</t>
+          <t>4451; 12555</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13643; 25540</t>
+          <t>14251; 25935</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>679; 6164</t>
+          <t>710; 6721</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4706</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3539; 11749</t>
+          <t>3015; 11669</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15057; 27453</t>
+          <t>16068; 28253</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1901; 8656</t>
+          <t>1827; 7964</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1343; 7790</t>
+          <t>1327; 7686</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9616; 21694</t>
+          <t>9056; 20333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32879; 49539</t>
+          <t>32560; 50086</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16400; 32157</t>
+          <t>16907; 32268</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13301; 27737</t>
+          <t>13942; 27840</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52474; 76550</t>
+          <t>52575; 75993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97962; 130127</t>
+          <t>97860; 129801</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15254; 30745</t>
+          <t>15294; 29676</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15175; 30432</t>
+          <t>15244; 30319</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>54971; 79762</t>
+          <t>55473; 80005</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>130012; 172178</t>
+          <t>130820; 173527</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35672; 55962</t>
+          <t>35957; 57070</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32507; 53488</t>
+          <t>33270; 53298</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113856; 149223</t>
+          <t>114743; 150367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>239240; 289143</t>
+          <t>240376; 289330</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C02-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,87%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,41%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>17,78%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,36</t>
+          <t>1,35; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,73</t>
+          <t>7,98; 26,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 29,0</t>
+          <t>6,93; 23,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,25; 38,88</t>
+          <t>24,22; 41,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,0</t>
+          <t>3,63; 15,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61; 25,58</t>
+          <t>1,17; 12,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 23,57</t>
+          <t>9,78; 28,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 38,15</t>
+          <t>20,96; 39,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,84</t>
+          <t>2,69; 10,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 15,33</t>
+          <t>4,97; 15,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,03; 22,82</t>
+          <t>10,03; 22,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,59; 34,99</t>
+          <t>25,0; 38,14</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>16,11%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,19</t>
+          <t>6,33; 24,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,52</t>
+          <t>1,29; 13,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 25,39</t>
+          <t>8,72; 25,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 41,97</t>
+          <t>19,49; 38,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 25,27</t>
+          <t>1,14; 14,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 15,42</t>
+          <t>1,28; 11,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 26,81</t>
+          <t>8,88; 25,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 36,81</t>
+          <t>23,27; 43,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 15,69</t>
+          <t>4,92; 15,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,97</t>
+          <t>2,12; 9,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 22,82</t>
+          <t>11,11; 23,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,32; 36,52</t>
+          <t>24,35; 39,64</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,5%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,21</t>
+          <t>1,58; 15,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 24,06</t>
+          <t>6,42; 27,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 48,57</t>
+          <t>22,65; 50,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,8</t>
+          <t>0,0; 9,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 28,65</t>
+          <t>3,87; 23,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 51,98</t>
+          <t>18,51; 55,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,7</t>
+          <t>0,6; 5,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,86</t>
+          <t>0,81; 7,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,03</t>
+          <t>7,63; 21,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,02; 44,48</t>
+          <t>25,42; 46,67</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,77%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>18,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 14,87</t>
+          <t>2,14; 9,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,86</t>
+          <t>3,25; 12,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 25,78</t>
+          <t>14,06; 27,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 31,52</t>
+          <t>21,48; 39,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,16</t>
+          <t>5,24; 14,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,73</t>
+          <t>5,23; 15,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 26,69</t>
+          <t>13,4; 25,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 37,22</t>
+          <t>16,88; 30,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,55</t>
+          <t>4,12; 9,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 12,49</t>
+          <t>5,21; 12,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,34; 24,35</t>
+          <t>15,24; 24,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 31,66</t>
+          <t>20,89; 32,09</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35,66%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,04%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>21,13%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27,84%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,08; 20,4</t>
+          <t>4,02; 15,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,89</t>
+          <t>1,75; 10,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 29,27</t>
+          <t>17,19; 33,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 38,04</t>
+          <t>24,09; 46,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 15,86</t>
+          <t>5,98; 19,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,86</t>
+          <t>1,77; 10,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 34,14</t>
+          <t>13,95; 30,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,56; 43,12</t>
+          <t>20,77; 40,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 15,4</t>
+          <t>6,52; 15,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 8,4</t>
+          <t>2,42; 8,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 29,06</t>
+          <t>17,59; 29,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,99; 38,37</t>
+          <t>26,3; 41,12</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,01%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23,76%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 12,11</t>
+          <t>1,89; 17,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 23,55</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,65; 38,51</t>
+          <t>10,28; 34,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31,76; 57,81</t>
+          <t>38,46; 67,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 18,81</t>
+          <t>1,13; 12,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>2,69; 23,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,37; 36,25</t>
+          <t>12,74; 38,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,41; 64,02</t>
+          <t>32,97; 60,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 10,52</t>
+          <t>2,43; 10,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,31</t>
+          <t>2,14; 12,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 31,38</t>
+          <t>14,48; 32,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,58; 56,28</t>
+          <t>40,58; 59,35</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19,15%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33,69%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,32%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>18,56%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,15%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,99</t>
+          <t>4,41; 8,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,29</t>
+          <t>4,62; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,17</t>
+          <t>15,77; 23,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,3; 33,56</t>
+          <t>29,25; 38,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,69</t>
+          <t>5,14; 10,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,84</t>
+          <t>3,88; 8,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,92; 22,96</t>
+          <t>15,31; 22,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27,33; 36,25</t>
+          <t>26,8; 35,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,58</t>
+          <t>5,32; 8,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 7,85</t>
+          <t>4,84; 8,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16,6; 21,75</t>
+          <t>16,69; 21,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,77; 33,43</t>
+          <t>29,68; 36,11</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5972</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7015</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28931</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4314</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2127</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7648</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20379</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5972</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7015</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>21285</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>50216</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1563; 8417</t>
+          <t>669; 6022</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>566; 5657</t>
+          <t>3263; 10681</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4239; 12475</t>
+          <t>3501; 12005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13818; 27907</t>
+          <t>21938; 37868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>660; 5430</t>
+          <t>1988; 8581</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2704; 10458</t>
+          <t>563; 5817</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3754; 11908</t>
+          <t>4205; 12255</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20190; 36659</t>
+          <t>14988; 28108</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2898; 11285</t>
+          <t>2799; 11250</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4506; 13664</t>
+          <t>4431; 13679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9379; 21348</t>
+          <t>9386; 20608</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37925; 58744</t>
+          <t>40529; 61811</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20696</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2148</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8981</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19686</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5130</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3046</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>42031</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>463; 5342</t>
+          <t>2345; 8945</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>612; 5473</t>
+          <t>684; 7245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4885; 14152</t>
+          <t>4710; 13730</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13884; 26313</t>
+          <t>13724; 27238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2483; 9363</t>
+          <t>461; 5770</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>685; 8183</t>
+          <t>606; 5696</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4980; 14486</t>
+          <t>4951; 14005</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13455; 26354</t>
+          <t>15181; 28212</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3799; 12165</t>
+          <t>3818; 12266</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2101; 10031</t>
+          <t>2134; 10039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12301; 25053</t>
+          <t>12200; 25733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31317; 49038</t>
+          <t>33028; 53774</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2071</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5157</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12334</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>533</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3579</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5157</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>22268</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2773</t>
+          <t>0; 3968</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>630; 5971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1604; 7488</t>
+          <t>2203; 9518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5006; 13565</t>
+          <t>7810; 17471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4105</t>
+          <t>0; 2761</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>626; 5490</t>
+          <t>0; 3896</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2276; 9828</t>
+          <t>1204; 7157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7973; 18849</t>
+          <t>5370; 15996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>538; 5037</t>
+          <t>532; 5140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>766; 6407</t>
+          <t>660; 6267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4538; 13761</t>
+          <t>4990; 14024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14777; 28550</t>
+          <t>16143; 29635</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20643</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35250</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8611</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>21045</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25749</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4504</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6672</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20643</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35121</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60870</t>
+          <t>59753</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4586; 14591</t>
+          <t>2061; 9236</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4464; 14467</t>
+          <t>3188; 12162</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15200; 28643</t>
+          <t>14606; 28690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18105; 35000</t>
+          <t>26274; 48563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1969; 8809</t>
+          <t>5138; 14640</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3197; 12471</t>
+          <t>4775; 14289</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14334; 27719</t>
+          <t>14889; 28761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25310; 47412</t>
+          <t>18408; 32946</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8481; 20498</t>
+          <t>8007; 19038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10006; 23634</t>
+          <t>9864; 22910</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32973; 52350</t>
+          <t>32764; 52370</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>48820; 75478</t>
+          <t>48326; 74251</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6249</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18234</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33532</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>6580</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3793</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>14611</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>19072</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6249</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3485</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>18234</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52950</t>
+          <t>54833</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3324; 11153</t>
+          <t>2819; 11039</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1441; 8129</t>
+          <t>1288; 7954</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9551; 20244</t>
+          <t>12646; 24811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13439; 26059</t>
+          <t>22652; 43277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2918; 11106</t>
+          <t>3267; 10847</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1269; 8003</t>
+          <t>1453; 8455</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12421; 25125</t>
+          <t>9645; 20819</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21221; 44497</t>
+          <t>14345; 28218</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8428; 19200</t>
+          <t>8130; 19068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3790; 13095</t>
+          <t>3767; 12959</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24624; 41482</t>
+          <t>25104; 41556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39481; 65880</t>
+          <t>42889; 67062</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6620</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>22729</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1647</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2247</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7745</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19719</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6620</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>45303</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>454; 4843</t>
+          <t>674; 6139</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>662; 5875</t>
+          <t>0; 4397</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4451; 12555</t>
+          <t>3309; 11229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14251; 25935</t>
+          <t>16831; 29688</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>710; 6721</t>
+          <t>453; 5104</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>670; 5982</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3015; 11669</t>
+          <t>4155; 12667</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16068; 28253</t>
+          <t>15600; 28546</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1827; 7964</t>
+          <t>1838; 8181</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1327; 7686</t>
+          <t>1334; 7781</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9056; 20333</t>
+          <t>9379; 21116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32560; 50086</t>
+          <t>36959; 54060</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>161</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>21888</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>22557</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>66743</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>153472</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>23661</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>19752</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>63609</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>113307</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>21888</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22557</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>66743</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>120932</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>263911</t>
+          <t>274403</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16907; 32268</t>
+          <t>15071; 29509</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13942; 27840</t>
+          <t>15845; 32140</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52575; 75993</t>
+          <t>54955; 80312</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97860; 129801</t>
+          <t>133258; 174903</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>15294; 29676</t>
+          <t>16599; 32296</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15244; 30319</t>
+          <t>13029; 26936</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55473; 80005</t>
+          <t>52478; 76357</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>130820; 173527</t>
+          <t>104819; 137759</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>35957; 57070</t>
+          <t>35379; 56137</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33270; 53298</t>
+          <t>32850; 54653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>114743; 150367</t>
+          <t>115345; 148685</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>240376; 289330</t>
+          <t>251316; 305771</t>
         </is>
       </c>
     </row>
